--- a/student_import_template.xlsx
+++ b/student_import_template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,10 @@
       <b val="1"/>
       <color rgb="0022358A"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,6 +98,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -515,16 +522,8 @@
           <t>91234567</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>ahmed.mohammed</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="4" t="inlineStr">
         <is>
           <t>الصف الأول</t>
@@ -8556,67 +8555,63 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>• اكتب كل طالب في سطر واحد في ورقة «الطلاب»، وابدأ من السطر الثاني (يمكن حذف سطر المثال).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>• اسم الطالب: الاسم كما سيظهر في المنصة.</t>
+          <t>• المطلوب فقط: اسم الطالب، الصف، الشعبة.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>• هاتف ولي الأمر: 8 أرقام بالضبط، مثل 91234567.</t>
+          <t>• هاتف ولي الأمر: اختياري، 8 أرقام بالضبط مثل 91234567.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>• اسم المستخدم: حروف إنجليزية صغيرة وأرقام، ويسمح بالنقطة والشرطة، من 3 إلى 30 حرفًا بدون مسافات، ولا يتكرر لطالبين. مثال: ahmed.mohammed</t>
+          <t>• اسم المستخدم: اتركه فارغًا وستعطي المنصة كل طالب رقمًا تلقائيًا (101001، 101002…) يكمل من آخر رقم مستخدم، فلا يتكرر.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>• الرقم السري: 6 خانات على الأقل.</t>
+          <t>• الرقم السري: اتركه فارغًا ليكون 123456 للجميع، أو اكتب رقمًا سريًا خاصًا (6 خانات على الأقل).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>• الصف: اختره من القائمة (روضة، تمهيدي، الصف الأول … الصف الرابع).</t>
+          <t>• الصف: اختره من القائمة (روضة، تمهيدي، الصف الأول … الصف الرابع). الشعبة: رقم من 1 إلى 4.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>• الشعبة: اختر رقمًا من 1 إلى 4.</t>
+          <t>• بعد التعبئة: من «إدارة الطلاب» اضغط «اختيار ملف Excel / PDF»، راجع المعاينة، ثم «إضافة الجميع».</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>• بعد التعبئة: من «إدارة الطلاب» اضغط «اختيار ملف Excel / PDF»، راجع المعاينة، ثم أكّد الإضافة.</t>
+          <t>• لطباعة أسماء المستخدمين والأرقام السرية: زر «طباعة بيانات الدخول» أعلى صفحة إدارة الطلاب.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>• يدخل الطالب إلى المنصة باسم المستخدم والرقم السري.</t>
-        </is>
-      </c>
+      <c r="A10" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
